--- a/Funding_impactAnalysis/data/used_subcountiesHIVselfkit.xlsx
+++ b/Funding_impactAnalysis/data/used_subcountiesHIVselfkit.xlsx
@@ -14,187 +14,187 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
-    <t xml:space="preserve">county_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sub_county_name</t>
+    <t xml:space="preserve">County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub county</t>
   </si>
   <si>
     <t xml:space="preserve">Baringo County</t>
   </si>
   <si>
-    <t xml:space="preserve">Marigat Sub County</t>
+    <t xml:space="preserve">marigat</t>
   </si>
   <si>
     <t xml:space="preserve">Bungoma County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kimilili Sub County</t>
+    <t xml:space="preserve">kimilili</t>
   </si>
   <si>
     <t xml:space="preserve">Elgeyo Marakwet County</t>
   </si>
   <si>
-    <t xml:space="preserve">Marakwet West Sub County</t>
+    <t xml:space="preserve">marakwet west</t>
   </si>
   <si>
     <t xml:space="preserve">Kiambu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Githunguri Sub County</t>
+    <t xml:space="preserve">githunguri</t>
   </si>
   <si>
     <t xml:space="preserve">Kilifi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaloleni Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilifi North Sub County</t>
+    <t xml:space="preserve">kaloleni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilifi north</t>
   </si>
   <si>
     <t xml:space="preserve">Kisii County</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyaribari Chache Sub County</t>
+    <t xml:space="preserve">nyaribari chache</t>
   </si>
   <si>
     <t xml:space="preserve">Kitui County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui East Sub County</t>
+    <t xml:space="preserve">kitui east</t>
   </si>
   <si>
     <t xml:space="preserve">Laikipia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laikipia North Sub County</t>
+    <t xml:space="preserve">laikipia east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laikipia north</t>
   </si>
   <si>
     <t xml:space="preserve">Machakos County</t>
   </si>
   <si>
-    <t xml:space="preserve">Machakos Sub County</t>
+    <t xml:space="preserve">machakos</t>
   </si>
   <si>
     <t xml:space="preserve">Makueni County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaiti Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makueni Sub County</t>
+    <t xml:space="preserve">kaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">makueni</t>
   </si>
   <si>
     <t xml:space="preserve">Mombasa County</t>
   </si>
   <si>
-    <t xml:space="preserve">Jomvu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mvita Sub County</t>
+    <t xml:space="preserve">jomvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvita</t>
   </si>
   <si>
     <t xml:space="preserve">Nakuru County</t>
   </si>
   <si>
-    <t xml:space="preserve">Naivasha Sub County</t>
+    <t xml:space="preserve">naivasha</t>
   </si>
   <si>
     <t xml:space="preserve">Nandi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldai Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emgwen Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tinderet Sub County</t>
+    <t xml:space="preserve">aldai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emgwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tinderet</t>
   </si>
   <si>
     <t xml:space="preserve">Narok County</t>
   </si>
   <si>
-    <t xml:space="preserve">Narok Central Sub County</t>
+    <t xml:space="preserve">narok central</t>
   </si>
   <si>
     <t xml:space="preserve">Nyandarua County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ndaragwa Sub County</t>
+    <t xml:space="preserve">ndaragwa</t>
   </si>
   <si>
     <t xml:space="preserve">Samburu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samburu East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samburu North Sub County</t>
+    <t xml:space="preserve">samburu central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samburu east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samburu north</t>
   </si>
   <si>
     <t xml:space="preserve">Siaya County</t>
   </si>
   <si>
-    <t xml:space="preserve">Alego Usonga Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bondo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gem Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugenya Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugunja Sub County</t>
+    <t xml:space="preserve">alego usonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ugenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ugunja</t>
   </si>
   <si>
     <t xml:space="preserve">Taita Taveta County</t>
   </si>
   <si>
-    <t xml:space="preserve">Voi Sub County</t>
+    <t xml:space="preserve">voi</t>
   </si>
   <si>
     <t xml:space="preserve">Tharaka Nithi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Maara Sub County</t>
+    <t xml:space="preserve">maara</t>
   </si>
   <si>
     <t xml:space="preserve">Turkana County</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana South Sub County</t>
+    <t xml:space="preserve">turkana central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana south</t>
   </si>
   <si>
     <t xml:space="preserve">Uasin Gishu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapseret Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soy Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turbo Sub County</t>
+    <t xml:space="preserve">kapseret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turbo</t>
   </si>
   <si>
     <t xml:space="preserve">Vihiga County</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamisi Sub County</t>
+    <t xml:space="preserve">hamisi</t>
   </si>
 </sst>
 </file>
